--- a/SB - Monica Logan.xlsx
+++ b/SB - Monica Logan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeremiah\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeremiah\Documents\GitHub\SMPW-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBD8917-BA35-495C-9000-794A600379FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF4D4A4-9DAC-4574-8F3E-FB9F938CB5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{17F5B227-8E88-5E47-AD89-2C3584B21BAD}"/>
+    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{17F5B227-8E88-5E47-AD89-2C3584B21BAD}"/>
   </bookViews>
   <sheets>
     <sheet name="Friday AM" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="357">
   <si>
     <t>Driver #</t>
   </si>
@@ -1105,6 +1105,9 @@
   </si>
   <si>
     <t>702-301-0647</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1206,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1216,14 +1219,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -1240,7 +1235,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1568,7 +1562,7 @@
   <dimension ref="A1:I58"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18" style="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.625" customWidth="1"/>
     <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.375" customWidth="1"/>
@@ -1579,7 +1573,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1606,7 +1600,7 @@
       <c r="I1"/>
     </row>
     <row r="2" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20">
+      <c r="A2" s="15">
         <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1624,7 +1618,7 @@
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="2">
         <v>2021</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -1633,13 +1627,13 @@
       <c r="I2"/>
     </row>
     <row r="3" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20">
+      <c r="A3" s="15">
         <v>20</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -1648,25 +1642,25 @@
       <c r="E3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I3"/>
     </row>
     <row r="4" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
+      <c r="A4" s="15">
         <v>14</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -1675,19 +1669,19 @@
       <c r="E4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I4"/>
     </row>
     <row r="5" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20">
+      <c r="A5" s="15">
         <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1702,36 +1696,34 @@
       <c r="E5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="G5" s="2"/>
       <c r="I5"/>
     </row>
     <row r="6" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="A6" s="15">
         <v>37</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9" t="s">
+      <c r="F6" s="3"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
         <v>34</v>
       </c>
       <c r="I6"/>
     </row>
     <row r="7" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20">
+      <c r="A7" s="15">
         <v>21</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1743,41 +1735,38 @@
       <c r="D7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I7"/>
     </row>
     <row r="8" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20">
+      <c r="A8" s="15">
         <v>22</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="G8" s="2"/>
       <c r="I8"/>
     </row>
     <row r="9" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20">
+      <c r="A9" s="15">
         <v>31</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1789,7 +1778,7 @@
       <c r="D9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -1804,7 +1793,7 @@
       <c r="I9"/>
     </row>
     <row r="10" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20">
+      <c r="A10" s="15">
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1816,47 +1805,44 @@
       <c r="D10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+      <c r="G10" s="2"/>
       <c r="I10"/>
     </row>
     <row r="11" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21">
+      <c r="A11" s="16">
         <v>15</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I11"/>
     </row>
     <row r="12" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20">
+      <c r="A12" s="15">
         <v>51</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -1865,100 +1851,100 @@
       <c r="E12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="4" t="s">
         <v>64</v>
       </c>
       <c r="I12"/>
     </row>
     <row r="13" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20">
+      <c r="A13" s="15">
         <v>43</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="4" t="s">
         <v>34</v>
       </c>
       <c r="I13"/>
     </row>
     <row r="14" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
+      <c r="A14" s="15">
         <v>47</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="2">
         <v>2021</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="2">
         <v>5</v>
       </c>
       <c r="I14"/>
     </row>
     <row r="15" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20">
+      <c r="A15" s="15">
         <v>45</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I15"/>
     </row>
     <row r="16" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
+      <c r="A16" s="15">
         <v>56</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -1970,41 +1956,38 @@
       <c r="D16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="4" t="s">
         <v>86</v>
       </c>
       <c r="I16"/>
     </row>
     <row r="17" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20">
+      <c r="A17" s="15">
         <v>48</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="3" t="s">
         <v>88</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="G17" s="2"/>
       <c r="I17"/>
     </row>
     <row r="18" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20">
+      <c r="A18" s="15">
         <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -2016,14 +1999,11 @@
       <c r="D18" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
+      <c r="G18" s="2"/>
       <c r="I18"/>
     </row>
     <row r="19" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20">
+      <c r="A19" s="15">
         <v>10</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -2035,22 +2015,22 @@
       <c r="D19" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I19"/>
     </row>
     <row r="20" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20">
+      <c r="A20" s="15">
         <v>23</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -2062,103 +2042,103 @@
       <c r="D20" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I20"/>
     </row>
     <row r="21" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20">
+      <c r="A21" s="15">
         <v>50</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="3" t="s">
         <v>96</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="4" t="s">
         <v>64</v>
       </c>
       <c r="I21"/>
     </row>
     <row r="22" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="20">
+      <c r="A22" s="15">
         <v>2</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="4" t="s">
         <v>34</v>
       </c>
       <c r="I22"/>
     </row>
     <row r="23" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="20">
+      <c r="A23" s="15">
         <v>13</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="4" t="s">
         <v>64</v>
       </c>
       <c r="I23"/>
     </row>
     <row r="24" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="20">
+      <c r="A24" s="15">
         <v>33</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -2170,14 +2150,11 @@
       <c r="D24" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+      <c r="G24" s="2"/>
       <c r="I24"/>
     </row>
     <row r="25" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="20">
+      <c r="A25" s="15">
         <v>26</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -2189,31 +2166,31 @@
       <c r="D25" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="4" t="s">
         <v>64</v>
       </c>
       <c r="I25"/>
     </row>
     <row r="26" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="20">
+      <c r="A26" s="15">
         <v>39</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -2222,16 +2199,16 @@
       <c r="F26" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I26"/>
     </row>
     <row r="27" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="20">
+      <c r="A27" s="15">
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -2243,14 +2220,11 @@
       <c r="D27" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="G27" s="2"/>
       <c r="I27"/>
     </row>
     <row r="28" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="20">
+      <c r="A28" s="15">
         <v>46</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -2262,72 +2236,67 @@
       <c r="D28" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="E28" s="3"/>
+      <c r="G28" s="2"/>
       <c r="I28"/>
     </row>
     <row r="29" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="20">
+      <c r="A29" s="15">
         <v>40</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I29"/>
     </row>
     <row r="30" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="20">
+      <c r="A30" s="15">
         <v>53</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
+      <c r="G30" s="2"/>
       <c r="I30"/>
     </row>
     <row r="31" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="20">
+      <c r="A31" s="15">
         <v>41</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="3" t="s">
         <v>145</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="3" t="s">
         <v>147</v>
       </c>
       <c r="F31" s="3" t="s">
@@ -2342,7 +2311,7 @@
       <c r="I31"/>
     </row>
     <row r="32" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20">
+      <c r="A32" s="15">
         <v>30</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -2354,22 +2323,22 @@
       <c r="D32" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="4" t="s">
         <v>64</v>
       </c>
       <c r="I32"/>
     </row>
     <row r="33" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20">
+      <c r="A33" s="15">
         <v>44</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -2381,49 +2350,49 @@
       <c r="D33" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I33"/>
     </row>
     <row r="34" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="20">
+      <c r="A34" s="15">
         <v>9</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="4" t="s">
         <v>34</v>
       </c>
       <c r="I34"/>
     </row>
     <row r="35" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="20">
+      <c r="A35" s="15">
         <v>1</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -2435,7 +2404,7 @@
       <c r="D35" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="3" t="s">
         <v>169</v>
       </c>
       <c r="F35" s="3" t="s">
@@ -2450,7 +2419,7 @@
       <c r="I35"/>
     </row>
     <row r="36" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="20">
+      <c r="A36" s="15">
         <v>55</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -2462,22 +2431,22 @@
       <c r="D36" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" t="s">
         <v>101</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="4" t="s">
         <v>166</v>
       </c>
       <c r="I36"/>
     </row>
     <row r="37" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="20">
+      <c r="A37" s="15">
         <v>4</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -2489,49 +2458,49 @@
       <c r="D37" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F37" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="2">
         <v>2018</v>
       </c>
-      <c r="H37" s="7">
+      <c r="H37" s="2">
         <v>6</v>
       </c>
       <c r="I37"/>
     </row>
     <row r="38" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="20">
+      <c r="A38" s="15">
         <v>25</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="3" t="s">
         <v>178</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="2">
         <v>2012</v>
       </c>
-      <c r="H38" s="7">
+      <c r="H38" s="2">
         <v>6</v>
       </c>
       <c r="I38"/>
     </row>
     <row r="39" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="20">
+      <c r="A39" s="15">
         <v>49</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -2543,18 +2512,17 @@
       <c r="D39" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="9" t="s">
+      <c r="G39" s="2"/>
+      <c r="H39" s="4" t="s">
         <v>34</v>
       </c>
       <c r="I39"/>
     </row>
     <row r="40" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="21">
+      <c r="A40" s="16">
         <v>42</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -2566,22 +2534,22 @@
       <c r="D40" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="H40" s="4" t="s">
         <v>34</v>
       </c>
       <c r="I40"/>
     </row>
     <row r="41" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="20">
+      <c r="A41" s="15">
         <v>34</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -2593,83 +2561,78 @@
       <c r="D41" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" t="s">
         <v>110</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="H41" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I41"/>
     </row>
     <row r="42" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="20">
+      <c r="A42" s="15">
         <v>12</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="8" t="s">
         <v>192</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7">
+      <c r="G42" s="2"/>
+      <c r="H42" s="2">
         <v>15</v>
       </c>
       <c r="I42"/>
     </row>
     <row r="43" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="20">
+      <c r="A43" s="15">
         <v>11</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="3" t="s">
         <v>194</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
+      <c r="E43" s="3"/>
+      <c r="G43" s="2"/>
       <c r="I43"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="22">
+      <c r="A44" s="17">
         <v>3</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="3" t="s">
         <v>197</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>198</v>
       </c>
       <c r="E44" s="3"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
+      <c r="G44" s="2"/>
       <c r="I44"/>
     </row>
     <row r="45" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="20">
+      <c r="A45" s="15">
         <v>5</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -2696,7 +2659,7 @@
       <c r="I45"/>
     </row>
     <row r="46" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="20">
+      <c r="A46" s="15">
         <v>8</v>
       </c>
       <c r="B46" s="3" t="s">
@@ -2711,19 +2674,19 @@
       <c r="E46" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="H46" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I46"/>
     </row>
     <row r="47" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="20">
+      <c r="A47" s="15">
         <v>16</v>
       </c>
       <c r="B47" s="3" t="s">
@@ -2735,22 +2698,22 @@
       <c r="D47" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" t="s">
         <v>101</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="H47" s="9" t="s">
+      <c r="H47" s="4" t="s">
         <v>166</v>
       </c>
       <c r="I47"/>
     </row>
     <row r="48" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="20">
+      <c r="A48" s="15">
         <v>35</v>
       </c>
       <c r="B48" s="3" t="s">
@@ -2762,22 +2725,22 @@
       <c r="D48" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="G48" s="13">
+      <c r="G48" s="9">
         <v>2017</v>
       </c>
-      <c r="H48" s="13">
+      <c r="H48" s="9">
         <v>4</v>
       </c>
       <c r="I48"/>
     </row>
     <row r="49" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="20">
+      <c r="A49" s="15">
         <v>38</v>
       </c>
       <c r="B49" s="3" t="s">
@@ -2789,76 +2752,76 @@
       <c r="D49" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="G49" s="13">
+      <c r="G49" s="9">
         <v>2020</v>
       </c>
-      <c r="H49" s="13">
+      <c r="H49" s="9">
         <v>7</v>
       </c>
       <c r="I49"/>
     </row>
     <row r="50" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="20">
+      <c r="A50" s="15">
         <v>28</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" t="s">
         <v>222</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="G50" s="13">
+      <c r="G50" s="9">
         <v>2016</v>
       </c>
-      <c r="H50" s="13">
+      <c r="H50" s="9">
         <v>4</v>
       </c>
       <c r="I50"/>
     </row>
     <row r="51" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="20">
+      <c r="A51" s="15">
         <v>29</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="7" t="s">
         <v>226</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="G51" s="13">
+      <c r="G51" s="9">
         <v>2017</v>
       </c>
-      <c r="H51" s="13">
+      <c r="H51" s="9">
         <v>5</v>
       </c>
       <c r="I51"/>
     </row>
     <row r="52" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="21">
+      <c r="A52" s="16">
         <v>19</v>
       </c>
       <c r="B52" s="3" t="s">
@@ -2870,14 +2833,13 @@
       <c r="D52" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="E52" s="6"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
       <c r="I52"/>
     </row>
     <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="21">
+      <c r="A53" s="16">
         <v>54</v>
       </c>
       <c r="B53" s="3" t="s">
@@ -2889,22 +2851,22 @@
       <c r="D53" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="F53" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="G53" s="7">
+      <c r="G53" s="2">
         <v>2016</v>
       </c>
-      <c r="H53" s="7">
+      <c r="H53" s="2">
         <v>4</v>
       </c>
       <c r="I53"/>
     </row>
     <row r="54" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="20">
+      <c r="A54" s="15">
         <v>7</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -2916,49 +2878,49 @@
       <c r="D54" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="F54" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="G54" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H54" s="9" t="s">
+      <c r="H54" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I54"/>
     </row>
     <row r="55" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="20">
+      <c r="A55" s="15">
         <v>52</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="3" t="s">
         <v>240</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E55" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="F55" s="8" t="s">
+      <c r="F55" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="G55" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="H55" s="9" t="s">
+      <c r="H55" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I55"/>
     </row>
     <row r="56" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="20">
+      <c r="A56" s="15">
         <v>17</v>
       </c>
       <c r="B56" s="3" t="s">
@@ -2970,14 +2932,12 @@
       <c r="D56" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="E56" s="8"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
+      <c r="E56" s="3"/>
+      <c r="H56"/>
       <c r="I56"/>
     </row>
     <row r="57" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="20">
+      <c r="A57" s="15">
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
@@ -2989,14 +2949,11 @@
       <c r="D57" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
+      <c r="G57" s="2"/>
       <c r="I57"/>
     </row>
     <row r="58" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="20">
+      <c r="A58" s="15">
         <v>36</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -3008,10 +2965,7 @@
       <c r="D58" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
+      <c r="G58" s="2"/>
       <c r="I58"/>
     </row>
   </sheetData>
@@ -3025,11 +2979,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F115B2DE-191E-412F-9DCC-C1D50EC9D9C4}">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -3054,8 +3008,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20">
+    <row r="2" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
         <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -3073,15 +3027,15 @@
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="2">
         <v>2021</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20">
+    <row r="3" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
         <v>20</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -3100,8 +3054,8 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
+    <row r="4" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -3113,7 +3067,7 @@
       <c r="D4" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" t="s">
         <v>110</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -3126,8 +3080,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20">
+    <row r="5" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
         <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -3142,18 +3096,18 @@
       <c r="E5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+    <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
         <v>37</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -3178,8 +3132,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20">
+    <row r="7" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
         <v>21</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -3204,8 +3158,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20">
+    <row r="8" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
         <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -3217,7 +3171,7 @@
       <c r="D8" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -3229,9 +3183,12 @@
       <c r="H8" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20">
+      <c r="M8" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
         <v>31</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -3256,17 +3213,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20">
+    <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="3" t="s">
         <v>268</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -3282,8 +3239,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21">
+    <row r="11" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16">
         <v>15</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -3308,8 +3265,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20">
+    <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
         <v>51</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -3321,21 +3278,21 @@
       <c r="D12" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" t="s">
         <v>62</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20">
+    <row r="13" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
         <v>43</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -3347,30 +3304,30 @@
       <c r="D13" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" t="s">
         <v>74</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="2">
         <v>2021</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
+    <row r="14" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15">
         <v>47</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="7" t="s">
         <v>278</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -3379,11 +3336,11 @@
       <c r="F14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20">
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15">
         <v>45</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -3395,7 +3352,7 @@
       <c r="D15" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="3" t="s">
         <v>147</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -3408,8 +3365,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
+    <row r="16" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="15">
         <v>56</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -3435,7 +3392,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20">
+      <c r="A17" s="15">
         <v>48</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -3447,38 +3404,37 @@
       <c r="D17" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20">
+      <c r="A18" s="15">
         <v>57</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20">
+      <c r="A19" s="15">
         <v>10</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -3504,13 +3460,13 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20">
+      <c r="A20" s="15">
         <v>23</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="3" t="s">
         <v>99</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -3519,18 +3475,18 @@
       <c r="E20" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20">
+      <c r="A21" s="15">
         <v>50</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -3556,7 +3512,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="20">
+      <c r="A22" s="15">
         <v>2</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -3582,7 +3538,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="20">
+      <c r="A23" s="15">
         <v>13</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -3606,7 +3562,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="20">
+      <c r="A24" s="15">
         <v>33</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -3632,7 +3588,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="20">
+      <c r="A25" s="15">
         <v>26</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -3658,7 +3614,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="20">
+      <c r="A26" s="15">
         <v>39</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -3684,7 +3640,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="20">
+      <c r="A27" s="15">
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -3710,7 +3666,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="20">
+      <c r="A28" s="15">
         <v>46</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -3722,25 +3678,24 @@
       <c r="D28" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="E28" s="6"/>
       <c r="F28" s="3"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="20">
+      <c r="A29" s="15">
         <v>40</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F29" s="3" t="s">
@@ -3754,13 +3709,13 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="20">
+      <c r="A30" s="15">
         <v>53</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="3" t="s">
         <v>305</v>
       </c>
       <c r="D30" s="3" t="s">
@@ -3769,18 +3724,18 @@
       <c r="E30" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="20">
+      <c r="A31" s="15">
         <v>41</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -3792,21 +3747,21 @@
       <c r="D31" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="10" t="s">
         <v>62</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="2">
         <v>2005</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20">
+      <c r="A32" s="15">
         <v>30</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -3832,7 +3787,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20">
+      <c r="A33" s="15">
         <v>44</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -3844,30 +3799,30 @@
       <c r="D33" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G33" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H33" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="20">
+      <c r="A34" s="15">
         <v>9</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="7" t="s">
         <v>322</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -3884,7 +3839,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="20">
+      <c r="A35" s="15">
         <v>1</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -3899,10 +3854,10 @@
       <c r="E35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="4" t="s">
         <v>106</v>
       </c>
       <c r="H35" s="4" t="s">
@@ -3910,7 +3865,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="20">
+      <c r="A36" s="15">
         <v>4</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -3922,12 +3877,12 @@
       <c r="D36" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E36" s="8"/>
+      <c r="E36" s="3"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
     <row r="37" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="20">
+      <c r="A37" s="15">
         <v>55</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -3940,12 +3895,11 @@
         <v>326</v>
       </c>
       <c r="E37" s="3"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
     </row>
     <row r="38" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="20">
+      <c r="A38" s="15">
         <v>25</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -3971,7 +3925,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="20">
+      <c r="A39" s="15">
         <v>49</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -3983,7 +3937,7 @@
       <c r="D39" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="3" t="s">
         <v>169</v>
       </c>
       <c r="F39" s="3" t="s">
@@ -3997,7 +3951,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="21">
+      <c r="A40" s="16">
         <v>42</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -4015,15 +3969,15 @@
       <c r="F40" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40" s="2">
         <v>2018</v>
       </c>
-      <c r="H40" s="7">
+      <c r="H40" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="20">
+      <c r="A41" s="15">
         <v>34</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -4038,14 +3992,13 @@
       <c r="E41" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="7"/>
+      <c r="G41" s="2"/>
       <c r="H41" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="20">
+      <c r="A42" s="15">
         <v>12</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -4057,21 +4010,21 @@
       <c r="D42" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="3" t="s">
         <v>178</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H42" s="9" t="s">
+      <c r="H42" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="20">
+      <c r="A43" s="15">
         <v>11</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -4089,15 +4042,15 @@
       <c r="F43" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G43" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H43" s="9" t="s">
+      <c r="H43" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="22">
+      <c r="A44" s="17">
         <v>3</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -4109,21 +4062,21 @@
       <c r="D44" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="3" t="s">
         <v>147</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H44" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="20">
+      <c r="A45" s="15">
         <v>5</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -4135,21 +4088,21 @@
       <c r="D45" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="F45" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="G45" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H45" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="20">
+      <c r="A46" s="15">
         <v>8</v>
       </c>
       <c r="B46" s="3" t="s">
@@ -4175,7 +4128,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="20">
+      <c r="A47" s="15">
         <v>16</v>
       </c>
       <c r="B47" s="3" t="s">
@@ -4201,25 +4154,23 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="20">
+      <c r="A48" s="15">
         <v>35</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
     <row r="49" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="20">
+      <c r="A49" s="15">
         <v>38</v>
       </c>
       <c r="B49" s="3" t="s">
@@ -4234,30 +4185,30 @@
       <c r="E49" t="s">
         <v>169</v>
       </c>
-      <c r="F49" s="8" t="s">
+      <c r="F49" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G49" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="H49" s="9" t="s">
+      <c r="H49" s="4" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="20">
+      <c r="A50" s="15">
         <v>28</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="11" t="s">
         <v>30</v>
       </c>
       <c r="F50" s="3"/>
@@ -4267,69 +4218,67 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="20">
+      <c r="A51" s="15">
         <v>29</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="6" t="s">
         <v>194</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>195</v>
       </c>
       <c r="E51" s="3"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
     </row>
     <row r="52" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="21">
+      <c r="A52" s="16">
         <v>19</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C52" s="6" t="s">
         <v>197</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E52" s="8"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
+      <c r="E52" s="3"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
     </row>
     <row r="53" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="21">
+      <c r="A53" s="16">
         <v>54</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="17" t="s">
+      <c r="F53" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G53" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H53" s="9" t="s">
+      <c r="H53" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="20">
+      <c r="A54" s="15">
         <v>7</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -4341,7 +4290,7 @@
       <c r="D54" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" t="s">
         <v>101</v>
       </c>
       <c r="F54" s="3" t="s">
@@ -4355,50 +4304,49 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="20">
+      <c r="A55" s="15">
         <v>52</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" t="s">
         <v>222</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="G55" s="13">
+      <c r="G55" s="9">
         <v>2016</v>
       </c>
-      <c r="H55" s="13">
+      <c r="H55" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="20">
+      <c r="A56" s="15">
         <v>17</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E56" s="6"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
     <row r="57" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="20">
+      <c r="A57" s="15">
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
@@ -4424,7 +4372,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="20">
+      <c r="A58" s="15">
         <v>36</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -4450,7 +4398,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="20">
+      <c r="A59" s="15">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -4459,7 +4407,7 @@
       <c r="C59" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="7" t="s">
         <v>355</v>
       </c>
       <c r="E59" s="3"/>
@@ -4468,7 +4416,7 @@
       <c r="H59" s="4"/>
     </row>
     <row r="60" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="20">
+      <c r="A60" s="15">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
@@ -4477,7 +4425,7 @@
       <c r="C60" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="3" t="s">
         <v>353</v>
       </c>
       <c r="E60" s="3" t="s">
